--- a/partner_results/ifnano/ClassMissingCurationStatus_ifnano.xlsx
+++ b/partner_results/ifnano/ClassMissingCurationStatus_ifnano.xlsx
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sample [ifnano]</t>
+          <t>laser-induced breakdown spectroscopy [ifnano]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A material entity, which is part of a larger set of the same material entity</t>
+          <t>Laser induced breakdown spectroscopy is a type of atomic emission spectroscopy which uses a highly energetic laser pulse as the excitation source. The laser is focused to form a plasma, which atomizes and excites samples. The Emission of these excited species is analyzed to identify and quantify the elements contained in the sample.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -469,22 +469,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>peak [ifnano]</t>
+          <t>styrene-butadiene rubber SBR [ifnano]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>synthetic rubber [dik]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sven Schwabe (IFNANO)</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>In Spectroscopy, peaks are features of a spectrum. A peak comprise a restricted region of a spectrum, which is absorbed or emitted with high intensity. It is defined as a local maximum in the spectrum.</t>
+          <t>Families of synthetic rubbers derived from styrene and butadiene.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -492,22 +492,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>normalization [ifnano]</t>
+          <t>raw spectrum [ifnano]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Sven Schwabe (IFNANO)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Scaling spectra in order to get all data on approximately the same scale.</t>
+          <t>Unprocessed data obtained from spectrometric devices</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -515,22 +515,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>polymer composition [ifnano]</t>
+          <t>geometry correction [ifnano]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>proportion</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Christoph Lenth</t>
+          <t>Jan Geweke</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The relative proportions of monomers that make up a particular chemical polymer (raw rubber).</t>
+          <t>In terms of digtal image procession: correction methods to compensate image errors caused by lense distorsion or perspective.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fluororubber FKM [ifnano]</t>
+          <t>hydrogenated nitrile rubber HNBR [ifnano]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Is a family of fluorocarbon-based fluoroelastomer materials that contain vinylidene fluoride as a monomer.</t>
+          <t>Highly Saturated Nitrile. A Higher performance solid rubber material than NBR, achieved through adding Hydrogen Atoms to the Butadiene Segments.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -561,12 +561,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>raw spectrum [ifnano]</t>
+          <t>zinc [ifnano]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Unprocessed data obtained from spectrometric devices</t>
+          <t>The chemical element zinc</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -584,22 +584,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>laser-induced breakdown spectroscopy [ifnano]</t>
+          <t>nitrile rubber NBR [ifnano]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>synthetic rubber [dik]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sven Schwabe (IFNANO)</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Laser induced breakdown spectroscopy is a type of atomic emission spectroscopy which uses a highly energetic laser pulse as the excitation source. The laser is focused to form a plasma, which atomizes and excites samples. The Emission of these excited species is analyzed to identify and quantify the elements contained in the sample.</t>
+          <t>Known as nitrile butadiene rubber and acrylonitrile butadiene rubber, is a synthetic rubber derived from acrylonitrile (ACN) and butadiene.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -607,22 +607,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>butadiene rubber BR [ifnano]</t>
+          <t>standard deviation [ifnano]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>synthetic rubber [dik]</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Sven Schwabe (IFNANO)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Polybutadiene [butadiene rubber BR] is a synthetic rubber. Polybutadiene rubber is a polymer formed from the polymerization of the monomer 1,3-butadiene. Polybutadiene has a high resistance to wear and is used especially in the manufacture of tires.</t>
+          <t>A measure of the amount of variation of a set of values.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -630,22 +630,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nitrile rubber NBR [ifnano]</t>
+          <t>FTIR spectroscopy [ifnano]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>synthetic rubber [dik]</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Yaman Alsalka (IFNANO)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Known as nitrile butadiene rubber and acrylonitrile butadiene rubber, is a synthetic rubber derived from acrylonitrile (ACN) and butadiene.</t>
+          <t>Fourier transform infrared involves the probing of matter with infrared radiation. It is based on periodic changes in dipole moments caused by molecular vibrations during the absorption of IR radiation and gives spectroscopic fingerprints.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -653,12 +653,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>functional group [ifnano]</t>
+          <t>butyl rubber BIIR [ifnano]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>object aggregate</t>
+          <t>synthetic rubber [dik]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>An atom or group of atoms within a molecule that has similar chemical properties whenever it appears in various compounds. Even if other parts of the molecule are quite different, certain functional groups tend to react in certain ways.</t>
+          <t>Is a synthetic rubber, a copolymer of isobutylene with isoprene</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -676,22 +676,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ATR-FTIR [ifnano]</t>
+          <t>normalization [ifnano]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yamen Alsalka (IFNANO)</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>An attenuated total reflection accessory operates by measuring the changes that occur in a totally internally reflected infrared beam when the beam comes into contact with a sample.</t>
+          <t>Scaling spectra in order to get all data on approximately the same scale.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -699,22 +699,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EPDM rubber [ifnano]</t>
+          <t>sample [ifnano]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>synthetic rubber [dik]</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Sven Schwabe (IFNANO)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EPDM rubber (ethylene propylene diene monomer rubber) is a type of synthetic rubber that is composed of ethylidene norbornene (ENB), dicyclopentadiene (DCPD), and vinyl norbornene (VNB).</t>
+          <t>A material entity, which is part of a larger set of the same material entity</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -722,22 +722,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>standard deviation [ifnano]</t>
+          <t>butadiene rubber BR [ifnano]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>measurement datum</t>
+          <t>synthetic rubber [dik]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sven Schwabe (IFNANO)</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A measure of the amount of variation of a set of values.</t>
+          <t>Polybutadiene [butadiene rubber BR] is a synthetic rubber. Polybutadiene rubber is a polymer formed from the polymerization of the monomer 1,3-butadiene. Polybutadiene has a high resistance to wear and is used especially in the manufacture of tires.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -745,22 +745,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>styrene-butadiene rubber SBR [ifnano]</t>
+          <t>raw rubber samples [ifnano]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>synthetic rubber [dik]</t>
+          <t>raw material [hsh]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Yamen Alsalka (IFNANO)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Families of synthetic rubbers derived from styrene and butadiene.</t>
+          <t>Natural and synthetic rubber materials that are modified and shaped into rubber products through the rubber extrusion process.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -768,22 +768,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mooney viscosity [ifnano]</t>
+          <t>photometry [ifnano]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Christoph Lenth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The viscosity of rubber using a standard test method and Mooney Viscometer.</t>
+          <t>Measurement method using visible light to analyse the property of a substance</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>photometry [ifnano]</t>
+          <t>ATR-FTIR [ifnano]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Christoph Lenth</t>
+          <t>Yamen Alsalka (IFNANO)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Measurement method using visible light to analyse the property of a substance</t>
+          <t>An attenuated total reflection accessory operates by measuring the changes that occur in a totally internally reflected infrared beam when the beam comes into contact with a sample.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -814,22 +814,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>spectrum [ifnano]</t>
+          <t>EPDM rubber [ifnano]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>synthetic rubber [dik]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Christoph Lenth</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A graph that shows the intensity of radiation at different wavelengths or the response of the atomic or molecular system to different wavelengths of the radiation</t>
+          <t>EPDM rubber (ethylene propylene diene monomer rubber) is a type of synthetic rubber that is composed of ethylidene norbornene (ENB), dicyclopentadiene (DCPD), and vinyl norbornene (VNB).</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -837,22 +837,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>processed spectrum [ifnano]</t>
+          <t>functional group [ifnano]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>object aggregate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sven Schwabe (IFNANO)</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Result of different mathematical processes conducted on raw Spectra. Processing steps include, e.g., normalization and baseline correction.</t>
+          <t>An atom or group of atoms within a molecule that has similar chemical properties whenever it appears in various compounds. Even if other parts of the molecule are quite different, certain functional groups tend to react in certain ways.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -860,12 +860,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>butyl rubber BIIR [ifnano]</t>
+          <t>fluororubber FKM [ifnano]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>synthetic rubber [dik]</t>
+          <t>rubber particle [chebi]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Is a synthetic rubber, a copolymer of isobutylene with isoprene</t>
+          <t>Is a family of fluorocarbon-based fluoroelastomer materials that contain vinylidene fluoride as a monomer.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -883,18 +883,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>photometric measurement process [ifnano]</t>
+          <t>raman spectrum [ifnano]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>information content entity</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Christoph Lenth</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Measurement using photometry</t>
+          <t>A graph presents a number of peaks, showing the intensity and wavelength position of the Raman scattered light, in which each peak corresponds to a specific molecular bond vibration.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -902,22 +906,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Raman spectroscopy [ifnano]</t>
+          <t>peak [ifnano]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgios Ctistis</t>
+          <t>Sven Schwabe (IFNANO)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A non-destructive light scattering technique that provides detailed information about the chemical structure upon the interaction of light with the chemical bonds within a material based on periodic changes of polarizabilities, usually manifested as energy loss (gain) with respect to the incident light.</t>
+          <t>In Spectroscopy, peaks are features of a spectrum. A peak comprise a restricted region of a spectrum, which is absorbed or emitted with high intensity. It is defined as a local maximum in the spectrum.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -925,22 +929,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>zinc [ifnano]</t>
+          <t>digital image processing [ifnano]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>metal atom</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Sven Schwabe (IFNANO)</t>
-        </is>
-      </c>
+          <t>plan specification</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>The chemical element zinc</t>
+          <t>The use of a digital computer to process digital images through an algorithm.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -948,7 +948,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>raman spectrum [ifnano]</t>
+          <t>processed spectrum [ifnano]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Christoph Lenth</t>
+          <t>Sven Schwabe (IFNANO)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A graph presents a number of peaks, showing the intensity and wavelength position of the Raman scattered light, in which each peak corresponds to a specific molecular bond vibration.</t>
+          <t>Result of different mathematical processes conducted on raw Spectra. Processing steps include, e.g., normalization and baseline correction.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -971,134 +971,134 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>distribution quality [ifnano]</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sven Schwabe (IFNANO)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A quality of a sample in terms of homogenity, or the distribution of concentration of a specific component in a mixture, in a macroscopic body.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>polyisoprene IR [ifnano]</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>synthetic rubber [dik]</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yamen Alsalka</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A synthetic cis-1,4-polyisoprene, made by the industrial polymerisation of isoprene.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Raman spectroscopy [ifnano]</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>plan specification</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Georgios Ctistis</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A non-destructive light scattering technique that provides detailed information about the chemical structure upon the interaction of light with the chemical bonds within a material based on periodic changes of polarizabilities, usually manifested as energy loss (gain) with respect to the incident light.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mooney viscosity [ifnano]</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yamen Alsalka</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>The viscosity of rubber using a standard test method and Mooney Viscometer.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>monomer [ifnano]</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>molecular entity</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Asubstance which is capable of forming covalent bonds with a
 sequence of additional like or unlike molecules under the conditions of the relevant polymerforming reaction used for the particular process</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>geometry correction [ifnano]</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>plan specification</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Jan Geweke</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>In terms of digtal image procession: correction methods to compensate image errors caused by lense distorsion or perspective.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>raw rubber samples [ifnano]</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>raw material [hsh]</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Yamen Alsalka (IFNANO)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Natural and synthetic rubber materials that are modified and shaped into rubber products through the rubber extrusion process.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>polyisoprene IR [ifnano]</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>synthetic rubber [dik]</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yamen Alsalka</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>A synthetic cis-1,4-polyisoprene, made by the industrial polymerisation of isoprene.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>hydrogenated nitrile rubber HNBR [ifnano]</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>rubber particle [chebi]</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Yamen Alsalka</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Highly Saturated Nitrile. A Higher performance solid rubber material than NBR, achieved through adding Hydrogen Atoms to the Butadiene Segments.</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FTIR spectroscopy [ifnano]</t>
+          <t>polymer composition [ifnano]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>proportion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yaman Alsalka (IFNANO)</t>
+          <t>Christoph Lenth</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fourier transform infrared involves the probing of matter with infrared radiation. It is based on periodic changes in dipole moments caused by molecular vibrations during the absorption of IR radiation and gives spectroscopic fingerprints.</t>
+          <t>The relative proportions of monomers that make up a particular chemical polymer (raw rubber).</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1106,22 +1106,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>distribution quality [ifnano]</t>
+          <t>photometric measurement process [ifnano]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Sven Schwabe (IFNANO)</t>
-        </is>
-      </c>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A quality of a sample in terms of homogenity, or the distribution of concentration of a specific component in a mixture, in a macroscopic body.</t>
+          <t>Measurement using photometry</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1129,18 +1125,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>digital image processing [ifnano]</t>
+          <t>spectrum [ifnano]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>plan specification</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>information content entity</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Christoph Lenth</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>The use of a digital computer to process digital images through an algorithm.</t>
+          <t>A graph that shows the intensity of radiation at different wavelengths or the response of the atomic or molecular system to different wavelengths of the radiation</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
